--- a/doc/tech/java/java_memory.xlsx
+++ b/doc/tech/java/java_memory.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10523"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/AndroidAboutDemos/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/doc/tech/java/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A743BC5-4BDB-914D-BBEA-0BDE94624AED}" xr6:coauthVersionLast="33" xr6:coauthVersionMax="33" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70B59FA-D1A1-5A4A-BB19-5E830D99E4CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-2780" windowWidth="38400" windowHeight="23540" xr2:uid="{EE9AEC80-B3D9-5D49-A4FB-6D7D1582B117}"/>
+    <workbookView xWindow="28800" yWindow="460" windowWidth="38400" windowHeight="23540" activeTab="4" xr2:uid="{EE9AEC80-B3D9-5D49-A4FB-6D7D1582B117}"/>
   </bookViews>
   <sheets>
     <sheet name="Java 内存模型" sheetId="1" r:id="rId1"/>
     <sheet name="RuntimeDataAreaDemo.java -&gt; tes" sheetId="2" r:id="rId2"/>
     <sheet name="TestString2-&gt;test()" sheetId="4" r:id="rId3"/>
+    <sheet name="Stack_Heap" sheetId="6" r:id="rId4"/>
+    <sheet name="hashCode" sheetId="8" r:id="rId5"/>
+    <sheet name="==与equals" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -277,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
   <si>
     <t>运行时常量池</t>
   </si>
@@ -421,13 +424,171 @@
   </si>
   <si>
     <t>TestString2-&gt;test()</t>
+  </si>
+  <si>
+    <t>Heap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int a = 3</t>
+  </si>
+  <si>
+    <t>ox000001</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Home</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆内存</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>栈内存</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox000025</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>s5</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox000024</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>s4</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox000023</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>s3</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox000022</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>s2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox000021</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>s1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>String s5 = new String("efg")</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>String s4 = newString("efg")</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>常量池</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>String s3 = new String("abc")</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>String s2 = "abc"</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>String s1 = "abc"</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>"efg"</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>"abc"</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Home</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>√，表示相等。</t>
+  </si>
+  <si>
+    <r>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，表示不相等。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>存入不同地址（链式结构）</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>╳</t>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>存入不同地址</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能插入</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储地址</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>equals()方法</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>hashCode值</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -512,8 +673,83 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,8 +822,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -825,11 +1073,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -956,6 +1317,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1049,30 +1431,83 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{10EAB324-54A1-D04D-809F-501627DE2600}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{96180C7C-CE07-0248-8A7E-13E11580A40C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2658,6 +3093,474 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="直接箭头连接符 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1199A230-B652-BC45-9CD3-5A2A28081A1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3311525" y="704850"/>
+          <a:ext cx="1990725" cy="2428875"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直接箭头连接符 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB23823F-3A58-D34E-BC1E-2E037EFA3736}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3254375" y="742950"/>
+          <a:ext cx="2263775" cy="2603500"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直接箭头连接符 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A43A1BD1-313C-EC4F-9974-2156AFA667EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3273425" y="3133725"/>
+          <a:ext cx="2057400" cy="444500"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104777</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直接箭头连接符 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDFF3310-5136-8347-819E-CCA674C02306}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6061075" y="1508125"/>
+          <a:ext cx="946150" cy="2457452"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直接箭头连接符 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F547B11-B05F-D946-B823-4E9B62EB6713}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3365500" y="3540125"/>
+          <a:ext cx="1946275" cy="203200"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直接箭头连接符 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{854F9062-CF63-A944-A0CF-A3729D6C5677}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3311525" y="3917950"/>
+          <a:ext cx="2000250" cy="66675"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>142876</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直接箭头连接符 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89E25BD7-0A10-2E43-B454-0A4859AD61FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6057900" y="1381126"/>
+          <a:ext cx="815976" cy="2206624"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9219032" cy="2895274"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{788ADC59-6E16-9747-86DF-2284C59B0047}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="720725" y="5118100"/>
+          <a:ext cx="9219032" cy="2895274"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直接箭头连接符 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A737F2AF-3371-3F44-95DF-3CB95627B819}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5651500" y="936625"/>
+          <a:ext cx="409575" cy="2120900"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2956,22 +3859,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E5A3C-E206-8247-A603-97CD72934A23}">
   <dimension ref="B3:W122"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" ht="17" thickBot="1"/>
+    <row r="4" spans="2:5">
       <c r="B4" s="10"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="12"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5">
       <c r="B5" s="13"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="2:5" ht="26" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="26">
       <c r="B6" s="13"/>
       <c r="C6" s="16" t="s">
         <v>1</v>
@@ -2979,90 +3882,90 @@
       <c r="D6" s="16"/>
       <c r="E6" s="15"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5">
       <c r="B7" s="13"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="15"/>
     </row>
-    <row r="8" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" ht="17" thickBot="1">
       <c r="B8" s="13"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5">
       <c r="B9" s="13"/>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="127"/>
+      <c r="D9" s="96"/>
       <c r="E9" s="15"/>
     </row>
-    <row r="10" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" ht="17" thickBot="1">
       <c r="B10" s="13"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="129"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="98"/>
       <c r="E10" s="15"/>
     </row>
-    <row r="11" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" ht="17" thickBot="1">
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="15"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5">
       <c r="B12" s="13"/>
-      <c r="C12" s="126" t="s">
+      <c r="C12" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="127"/>
+      <c r="D12" s="96"/>
       <c r="E12" s="15"/>
     </row>
-    <row r="13" spans="2:5" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" ht="17" customHeight="1" thickBot="1">
       <c r="B13" s="13"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="129"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="98"/>
       <c r="E13" s="15"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5">
       <c r="B14" s="13"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="15"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5">
       <c r="B15" s="13"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="15"/>
     </row>
-    <row r="16" spans="2:5" ht="26" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5" ht="26">
       <c r="B16" s="13"/>
-      <c r="C16" s="125" t="s">
+      <c r="C16" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="125"/>
+      <c r="D16" s="94"/>
       <c r="E16" s="15"/>
     </row>
-    <row r="17" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:23" ht="17" thickBot="1">
       <c r="B17" s="13"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="15"/>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:23">
       <c r="B18" s="13"/>
-      <c r="C18" s="126" t="s">
+      <c r="C18" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="127"/>
+      <c r="D18" s="96"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" ht="17" thickBot="1">
       <c r="B19" s="13"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="129"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="98"/>
       <c r="E19" s="15"/>
       <c r="M19" s="40"/>
       <c r="N19" s="40"/>
@@ -3076,7 +3979,7 @@
       <c r="V19" s="40"/>
       <c r="W19" s="40"/>
     </row>
-    <row r="20" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" ht="17" thickBot="1">
       <c r="B20" s="17"/>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
@@ -3093,7 +3996,7 @@
       <c r="V20" s="40"/>
       <c r="W20" s="40"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:23">
       <c r="M21" s="40"/>
       <c r="N21" s="40"/>
       <c r="O21" s="40"/>
@@ -3106,7 +4009,7 @@
       <c r="V21" s="40"/>
       <c r="W21" s="40"/>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:23">
       <c r="M22" s="40"/>
       <c r="N22" s="40"/>
       <c r="O22" s="40"/>
@@ -3119,7 +4022,7 @@
       <c r="V22" s="40"/>
       <c r="W22" s="40"/>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:23">
       <c r="M23" s="40"/>
       <c r="N23" s="40"/>
       <c r="O23" s="40"/>
@@ -3132,7 +4035,7 @@
       <c r="V23" s="40"/>
       <c r="W23" s="40"/>
     </row>
-    <row r="24" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:23" ht="17" thickBot="1">
       <c r="M24" s="40"/>
       <c r="N24" s="41"/>
       <c r="O24" s="41"/>
@@ -3145,7 +4048,7 @@
       <c r="V24" s="40"/>
       <c r="W24" s="40"/>
     </row>
-    <row r="25" spans="2:23" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:23" ht="17" customHeight="1">
       <c r="B25" s="32"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
@@ -3163,7 +4066,7 @@
       <c r="T25" s="40"/>
       <c r="U25" s="40"/>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:23">
       <c r="B26" s="35"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31" t="s">
@@ -3183,7 +4086,7 @@
       <c r="T26" s="40"/>
       <c r="U26" s="40"/>
     </row>
-    <row r="27" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" ht="17" thickBot="1">
       <c r="B27" s="35"/>
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
@@ -3201,13 +4104,13 @@
       <c r="T27" s="40"/>
       <c r="U27" s="40"/>
     </row>
-    <row r="28" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:23" ht="17" thickBot="1">
       <c r="B28" s="35"/>
-      <c r="C28" s="104" t="s">
+      <c r="C28" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="105"/>
-      <c r="E28" s="106"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="113"/>
       <c r="F28" s="36"/>
       <c r="K28" s="40"/>
       <c r="L28" s="41"/>
@@ -3221,7 +4124,7 @@
       <c r="T28" s="40"/>
       <c r="U28" s="40"/>
     </row>
-    <row r="29" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:23" ht="17" thickBot="1">
       <c r="B29" s="35"/>
       <c r="C29" s="46"/>
       <c r="D29" s="46"/>
@@ -3239,13 +4142,13 @@
       <c r="T29" s="40"/>
       <c r="U29" s="40"/>
     </row>
-    <row r="30" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:23" ht="17" thickBot="1">
       <c r="B30" s="35"/>
-      <c r="C30" s="107" t="s">
+      <c r="C30" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="108"/>
-      <c r="E30" s="109"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="116"/>
       <c r="F30" s="36"/>
       <c r="K30" s="40"/>
       <c r="L30" s="41"/>
@@ -3259,7 +4162,7 @@
       <c r="T30" s="40"/>
       <c r="U30" s="40"/>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:23">
       <c r="B31" s="35"/>
       <c r="C31" s="47"/>
       <c r="D31" s="47"/>
@@ -3277,7 +4180,7 @@
       <c r="T31" s="40"/>
       <c r="U31" s="40"/>
     </row>
-    <row r="32" spans="2:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:23" ht="17" thickBot="1">
       <c r="B32" s="37"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
@@ -3295,7 +4198,7 @@
       <c r="T32" s="40"/>
       <c r="U32" s="40"/>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23">
       <c r="M33" s="40"/>
       <c r="N33" s="40"/>
       <c r="O33" s="40"/>
@@ -3308,7 +4211,7 @@
       <c r="V33" s="40"/>
       <c r="W33" s="40"/>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23">
       <c r="M34" s="40"/>
       <c r="N34" s="40"/>
       <c r="O34" s="40"/>
@@ -3321,7 +4224,7 @@
       <c r="V34" s="40"/>
       <c r="W34" s="40"/>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:23">
       <c r="M35" s="40"/>
       <c r="N35" s="40"/>
       <c r="O35" s="40"/>
@@ -3334,7 +4237,7 @@
       <c r="V35" s="40"/>
       <c r="W35" s="40"/>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:23">
       <c r="B36" s="48"/>
       <c r="C36" s="48"/>
       <c r="D36" s="48"/>
@@ -3356,7 +4259,7 @@
       <c r="U36" s="40"/>
       <c r="V36" s="40"/>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23">
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
       <c r="D37" s="49" t="s">
@@ -3380,7 +4283,7 @@
       <c r="U37" s="40"/>
       <c r="V37" s="40"/>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23">
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
       <c r="D38" s="48"/>
@@ -3402,7 +4305,7 @@
       <c r="U38" s="40"/>
       <c r="V38" s="40"/>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23">
       <c r="B39" s="48"/>
       <c r="C39" s="48"/>
       <c r="D39" s="48"/>
@@ -3416,7 +4319,7 @@
       <c r="M39" s="40"/>
       <c r="N39" s="40"/>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:23">
       <c r="B40" s="48"/>
       <c r="C40" s="48"/>
       <c r="D40" s="48"/>
@@ -3424,62 +4327,62 @@
       <c r="F40" s="48"/>
       <c r="G40" s="48"/>
       <c r="I40" s="40"/>
-      <c r="J40" s="113"/>
-      <c r="K40" s="113"/>
-      <c r="L40" s="113"/>
-      <c r="M40" s="113"/>
+      <c r="J40" s="120"/>
+      <c r="K40" s="120"/>
+      <c r="L40" s="120"/>
+      <c r="M40" s="120"/>
       <c r="N40" s="40"/>
     </row>
-    <row r="41" spans="2:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:23" ht="16" customHeight="1">
       <c r="B41" s="48"/>
-      <c r="C41" s="111" t="s">
+      <c r="C41" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="111"/>
-      <c r="E41" s="111"/>
-      <c r="F41" s="111"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
       <c r="G41" s="48"/>
       <c r="I41" s="40"/>
-      <c r="J41" s="113"/>
-      <c r="K41" s="113"/>
-      <c r="L41" s="113"/>
-      <c r="M41" s="113"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="120"/>
+      <c r="M41" s="120"/>
       <c r="N41" s="40"/>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23">
       <c r="B42" s="48"/>
-      <c r="C42" s="111"/>
-      <c r="D42" s="111"/>
-      <c r="E42" s="111"/>
-      <c r="F42" s="111"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
       <c r="G42" s="48"/>
       <c r="I42" s="40"/>
-      <c r="J42" s="113"/>
-      <c r="K42" s="113"/>
-      <c r="L42" s="113"/>
-      <c r="M42" s="113"/>
+      <c r="J42" s="120"/>
+      <c r="K42" s="120"/>
+      <c r="L42" s="120"/>
+      <c r="M42" s="120"/>
       <c r="N42" s="40"/>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23">
       <c r="B43" s="48"/>
-      <c r="C43" s="111"/>
-      <c r="D43" s="111"/>
-      <c r="E43" s="111"/>
-      <c r="F43" s="111"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="48"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="113"/>
-      <c r="K43" s="113"/>
-      <c r="L43" s="113"/>
-      <c r="M43" s="113"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="120"/>
+      <c r="L43" s="120"/>
+      <c r="M43" s="120"/>
       <c r="N43" s="40"/>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23">
       <c r="B44" s="48"/>
-      <c r="C44" s="111"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="111"/>
+      <c r="C44" s="118"/>
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="118"/>
       <c r="G44" s="48"/>
       <c r="I44" s="40"/>
       <c r="J44" s="40"/>
@@ -3488,7 +4391,7 @@
       <c r="M44" s="40"/>
       <c r="N44" s="40"/>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23">
       <c r="B45" s="48"/>
       <c r="C45" s="48"/>
       <c r="D45" s="48"/>
@@ -3502,7 +4405,7 @@
       <c r="M45" s="40"/>
       <c r="N45" s="40"/>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23">
       <c r="B46" s="48"/>
       <c r="C46" s="48"/>
       <c r="D46" s="48"/>
@@ -3516,14 +4419,14 @@
       <c r="M46" s="40"/>
       <c r="N46" s="40"/>
     </row>
-    <row r="47" spans="2:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" ht="16" customHeight="1">
       <c r="B47" s="48"/>
-      <c r="C47" s="111" t="s">
+      <c r="C47" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="48"/>
       <c r="I47" s="40"/>
       <c r="J47" s="40"/>
@@ -3532,31 +4435,31 @@
       <c r="M47" s="40"/>
       <c r="N47" s="40"/>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23">
       <c r="B48" s="48"/>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="111"/>
-      <c r="F48" s="111"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
       <c r="G48" s="48"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:7">
       <c r="B49" s="48"/>
-      <c r="C49" s="111"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="111"/>
-      <c r="F49" s="111"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="118"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
       <c r="G49" s="48"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:7">
       <c r="B50" s="48"/>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
-      <c r="E50" s="111"/>
-      <c r="F50" s="111"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="118"/>
       <c r="G50" s="48"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:7">
       <c r="B51" s="48"/>
       <c r="C51" s="48"/>
       <c r="D51" s="48"/>
@@ -3564,7 +4467,7 @@
       <c r="F51" s="48"/>
       <c r="G51" s="48"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:7">
       <c r="B52" s="48"/>
       <c r="C52" s="48"/>
       <c r="D52" s="48"/>
@@ -3572,17 +4475,17 @@
       <c r="F52" s="48"/>
       <c r="G52" s="48"/>
     </row>
-    <row r="53" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:7" ht="26">
       <c r="B53" s="48"/>
-      <c r="C53" s="112" t="s">
+      <c r="C53" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D53" s="112"/>
-      <c r="E53" s="112"/>
-      <c r="F53" s="112"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="119"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="48"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:7">
       <c r="B54" s="48"/>
       <c r="C54" s="48"/>
       <c r="D54" s="48"/>
@@ -3590,41 +4493,41 @@
       <c r="F54" s="48"/>
       <c r="G54" s="48"/>
     </row>
-    <row r="55" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:7" ht="16" customHeight="1">
       <c r="B55" s="48"/>
-      <c r="C55" s="111" t="s">
+      <c r="C55" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="111"/>
-      <c r="E55" s="111"/>
-      <c r="F55" s="111"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="118"/>
       <c r="G55" s="48"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:7">
       <c r="B56" s="48"/>
-      <c r="C56" s="111"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="111"/>
-      <c r="F56" s="111"/>
+      <c r="C56" s="118"/>
+      <c r="D56" s="118"/>
+      <c r="E56" s="118"/>
+      <c r="F56" s="118"/>
       <c r="G56" s="48"/>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:7">
       <c r="B57" s="48"/>
-      <c r="C57" s="111"/>
-      <c r="D57" s="111"/>
-      <c r="E57" s="111"/>
-      <c r="F57" s="111"/>
+      <c r="C57" s="118"/>
+      <c r="D57" s="118"/>
+      <c r="E57" s="118"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="48"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:7">
       <c r="B58" s="48"/>
-      <c r="C58" s="111"/>
-      <c r="D58" s="111"/>
-      <c r="E58" s="111"/>
-      <c r="F58" s="111"/>
+      <c r="C58" s="118"/>
+      <c r="D58" s="118"/>
+      <c r="E58" s="118"/>
+      <c r="F58" s="118"/>
       <c r="G58" s="48"/>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:7">
       <c r="B59" s="48"/>
       <c r="C59" s="48"/>
       <c r="D59" s="48"/>
@@ -3632,7 +4535,7 @@
       <c r="F59" s="48"/>
       <c r="G59" s="48"/>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:7">
       <c r="B60" s="48"/>
       <c r="C60" s="48"/>
       <c r="D60" s="48"/>
@@ -3640,7 +4543,7 @@
       <c r="F60" s="48"/>
       <c r="G60" s="48"/>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7">
       <c r="B61" s="48"/>
       <c r="C61" s="48"/>
       <c r="D61" s="48"/>
@@ -3648,8 +4551,8 @@
       <c r="F61" s="48"/>
       <c r="G61" s="48"/>
     </row>
-    <row r="62" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:7" ht="17" thickBot="1"/>
+    <row r="63" spans="2:7">
       <c r="B63" s="20"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
@@ -3657,7 +4560,7 @@
       <c r="F63" s="21"/>
       <c r="G63" s="22"/>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:7">
       <c r="B64" s="23"/>
       <c r="C64" s="24"/>
       <c r="D64" s="24" t="s">
@@ -3667,7 +4570,7 @@
       <c r="F64" s="24"/>
       <c r="G64" s="25"/>
     </row>
-    <row r="65" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" ht="17" thickBot="1">
       <c r="B65" s="23"/>
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
@@ -3675,25 +4578,25 @@
       <c r="F65" s="24"/>
       <c r="G65" s="25"/>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:7">
       <c r="B66" s="23"/>
-      <c r="C66" s="114" t="s">
+      <c r="C66" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="115"/>
-      <c r="E66" s="115"/>
-      <c r="F66" s="116"/>
+      <c r="D66" s="122"/>
+      <c r="E66" s="122"/>
+      <c r="F66" s="123"/>
       <c r="G66" s="25"/>
     </row>
-    <row r="67" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:7" ht="17" thickBot="1">
       <c r="B67" s="23"/>
-      <c r="C67" s="117"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="118"/>
-      <c r="F67" s="119"/>
+      <c r="C67" s="124"/>
+      <c r="D67" s="125"/>
+      <c r="E67" s="125"/>
+      <c r="F67" s="126"/>
       <c r="G67" s="25"/>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:7">
       <c r="B68" s="23"/>
       <c r="C68" s="24"/>
       <c r="D68" s="24"/>
@@ -3701,7 +4604,7 @@
       <c r="F68" s="24"/>
       <c r="G68" s="25"/>
     </row>
-    <row r="69" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" ht="17" thickBot="1">
       <c r="B69" s="23"/>
       <c r="C69" s="24"/>
       <c r="D69" s="24"/>
@@ -3709,25 +4612,25 @@
       <c r="F69" s="24"/>
       <c r="G69" s="25"/>
     </row>
-    <row r="70" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:7" ht="16" customHeight="1">
       <c r="B70" s="23"/>
-      <c r="C70" s="114" t="s">
+      <c r="C70" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="120"/>
-      <c r="E70" s="120"/>
-      <c r="F70" s="121"/>
+      <c r="D70" s="127"/>
+      <c r="E70" s="127"/>
+      <c r="F70" s="128"/>
       <c r="G70" s="25"/>
     </row>
-    <row r="71" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" ht="17" thickBot="1">
       <c r="B71" s="23"/>
-      <c r="C71" s="122"/>
-      <c r="D71" s="123"/>
-      <c r="E71" s="123"/>
-      <c r="F71" s="124"/>
+      <c r="C71" s="129"/>
+      <c r="D71" s="130"/>
+      <c r="E71" s="130"/>
+      <c r="F71" s="131"/>
       <c r="G71" s="25"/>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:7">
       <c r="B72" s="23"/>
       <c r="C72" s="24"/>
       <c r="D72" s="24"/>
@@ -3735,7 +4638,7 @@
       <c r="F72" s="24"/>
       <c r="G72" s="25"/>
     </row>
-    <row r="73" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" ht="17" thickBot="1">
       <c r="B73" s="23"/>
       <c r="C73" s="24"/>
       <c r="D73" s="24"/>
@@ -3743,25 +4646,25 @@
       <c r="F73" s="24"/>
       <c r="G73" s="25"/>
     </row>
-    <row r="74" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:7" ht="16" customHeight="1">
       <c r="B74" s="23"/>
-      <c r="C74" s="114" t="s">
+      <c r="C74" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="120"/>
-      <c r="E74" s="120"/>
-      <c r="F74" s="121"/>
+      <c r="D74" s="127"/>
+      <c r="E74" s="127"/>
+      <c r="F74" s="128"/>
       <c r="G74" s="25"/>
     </row>
-    <row r="75" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" ht="17" thickBot="1">
       <c r="B75" s="23"/>
-      <c r="C75" s="122"/>
-      <c r="D75" s="123"/>
-      <c r="E75" s="123"/>
-      <c r="F75" s="124"/>
+      <c r="C75" s="129"/>
+      <c r="D75" s="130"/>
+      <c r="E75" s="130"/>
+      <c r="F75" s="131"/>
       <c r="G75" s="25"/>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:7">
       <c r="B76" s="23"/>
       <c r="C76" s="24"/>
       <c r="D76" s="24"/>
@@ -3769,7 +4672,7 @@
       <c r="F76" s="24"/>
       <c r="G76" s="25"/>
     </row>
-    <row r="77" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" ht="17" thickBot="1">
       <c r="B77" s="23"/>
       <c r="C77" s="24"/>
       <c r="D77" s="24"/>
@@ -3777,25 +4680,25 @@
       <c r="F77" s="24"/>
       <c r="G77" s="25"/>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:7">
       <c r="B78" s="23"/>
-      <c r="C78" s="114" t="s">
+      <c r="C78" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="120"/>
-      <c r="E78" s="120"/>
-      <c r="F78" s="121"/>
+      <c r="D78" s="127"/>
+      <c r="E78" s="127"/>
+      <c r="F78" s="128"/>
       <c r="G78" s="25"/>
     </row>
-    <row r="79" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" ht="17" thickBot="1">
       <c r="B79" s="23"/>
-      <c r="C79" s="122"/>
-      <c r="D79" s="123"/>
-      <c r="E79" s="123"/>
-      <c r="F79" s="124"/>
+      <c r="C79" s="129"/>
+      <c r="D79" s="130"/>
+      <c r="E79" s="130"/>
+      <c r="F79" s="131"/>
       <c r="G79" s="25"/>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:7">
       <c r="B80" s="23"/>
       <c r="C80" s="24"/>
       <c r="D80" s="24"/>
@@ -3803,7 +4706,7 @@
       <c r="F80" s="24"/>
       <c r="G80" s="25"/>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:12">
       <c r="B81" s="23"/>
       <c r="C81" s="24"/>
       <c r="D81" s="24"/>
@@ -3811,7 +4714,7 @@
       <c r="F81" s="24"/>
       <c r="G81" s="25"/>
     </row>
-    <row r="82" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:12" ht="17" thickBot="1">
       <c r="B82" s="26"/>
       <c r="C82" s="27"/>
       <c r="D82" s="27"/>
@@ -3819,8 +4722,8 @@
       <c r="F82" s="27"/>
       <c r="G82" s="28"/>
     </row>
-    <row r="90" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:12" ht="17" thickBot="1"/>
+    <row r="91" spans="2:12">
       <c r="B91" s="1"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -3833,7 +4736,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="3"/>
     </row>
-    <row r="92" spans="2:12" ht="26" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:12" ht="26">
       <c r="B92" s="4"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
@@ -3848,7 +4751,7 @@
       <c r="K92" s="5"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:12" ht="17" thickBot="1">
       <c r="B93" s="4"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -3861,63 +4764,63 @@
       <c r="K93" s="5"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:12" ht="18" customHeight="1">
       <c r="B94" s="4"/>
-      <c r="C94" s="95" t="s">
+      <c r="C94" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D94" s="96"/>
-      <c r="E94" s="96"/>
-      <c r="F94" s="97"/>
+      <c r="D94" s="103"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="104"/>
       <c r="G94" s="5"/>
-      <c r="H94" s="110" t="s">
+      <c r="H94" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="I94" s="110"/>
-      <c r="J94" s="110"/>
-      <c r="K94" s="110"/>
+      <c r="I94" s="117"/>
+      <c r="J94" s="117"/>
+      <c r="K94" s="117"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:12">
       <c r="B95" s="4"/>
-      <c r="C95" s="98"/>
-      <c r="D95" s="99"/>
-      <c r="E95" s="99"/>
-      <c r="F95" s="100"/>
+      <c r="C95" s="105"/>
+      <c r="D95" s="106"/>
+      <c r="E95" s="106"/>
+      <c r="F95" s="107"/>
       <c r="G95" s="5"/>
-      <c r="H95" s="110"/>
-      <c r="I95" s="110"/>
-      <c r="J95" s="110"/>
-      <c r="K95" s="110"/>
+      <c r="H95" s="117"/>
+      <c r="I95" s="117"/>
+      <c r="J95" s="117"/>
+      <c r="K95" s="117"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:12">
       <c r="B96" s="4"/>
-      <c r="C96" s="98"/>
-      <c r="D96" s="99"/>
-      <c r="E96" s="99"/>
-      <c r="F96" s="100"/>
+      <c r="C96" s="105"/>
+      <c r="D96" s="106"/>
+      <c r="E96" s="106"/>
+      <c r="F96" s="107"/>
       <c r="G96" s="5"/>
-      <c r="H96" s="110"/>
-      <c r="I96" s="110"/>
-      <c r="J96" s="110"/>
-      <c r="K96" s="110"/>
+      <c r="H96" s="117"/>
+      <c r="I96" s="117"/>
+      <c r="J96" s="117"/>
+      <c r="K96" s="117"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:12" ht="17" thickBot="1">
       <c r="B97" s="4"/>
-      <c r="C97" s="101"/>
-      <c r="D97" s="102"/>
-      <c r="E97" s="102"/>
-      <c r="F97" s="103"/>
+      <c r="C97" s="108"/>
+      <c r="D97" s="109"/>
+      <c r="E97" s="109"/>
+      <c r="F97" s="110"/>
       <c r="G97" s="5"/>
-      <c r="H97" s="110"/>
-      <c r="I97" s="110"/>
-      <c r="J97" s="110"/>
-      <c r="K97" s="110"/>
+      <c r="H97" s="117"/>
+      <c r="I97" s="117"/>
+      <c r="J97" s="117"/>
+      <c r="K97" s="117"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:12">
       <c r="B98" s="4"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -3930,7 +4833,7 @@
       <c r="K98" s="5"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:12">
       <c r="B99" s="4"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -3943,7 +4846,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:12">
       <c r="B100" s="4"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
@@ -3956,50 +4859,50 @@
       <c r="K100" s="5"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:12">
       <c r="B101" s="4"/>
-      <c r="C101" s="131" t="s">
+      <c r="C101" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="D101" s="131"/>
-      <c r="E101" s="131"/>
-      <c r="F101" s="131"/>
+      <c r="D101" s="100"/>
+      <c r="E101" s="100"/>
+      <c r="F101" s="100"/>
       <c r="G101" s="5"/>
-      <c r="H101" s="94" t="s">
+      <c r="H101" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="I101" s="94"/>
-      <c r="J101" s="94"/>
-      <c r="K101" s="94"/>
+      <c r="I101" s="101"/>
+      <c r="J101" s="101"/>
+      <c r="K101" s="101"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:12">
       <c r="B102" s="4"/>
-      <c r="C102" s="131"/>
-      <c r="D102" s="131"/>
-      <c r="E102" s="131"/>
-      <c r="F102" s="131"/>
+      <c r="C102" s="100"/>
+      <c r="D102" s="100"/>
+      <c r="E102" s="100"/>
+      <c r="F102" s="100"/>
       <c r="G102" s="5"/>
-      <c r="H102" s="94"/>
-      <c r="I102" s="94"/>
-      <c r="J102" s="94"/>
-      <c r="K102" s="94"/>
+      <c r="H102" s="101"/>
+      <c r="I102" s="101"/>
+      <c r="J102" s="101"/>
+      <c r="K102" s="101"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:12">
       <c r="B103" s="4"/>
-      <c r="C103" s="131"/>
-      <c r="D103" s="131"/>
-      <c r="E103" s="131"/>
-      <c r="F103" s="131"/>
+      <c r="C103" s="100"/>
+      <c r="D103" s="100"/>
+      <c r="E103" s="100"/>
+      <c r="F103" s="100"/>
       <c r="G103" s="5"/>
-      <c r="H103" s="94"/>
-      <c r="I103" s="94"/>
-      <c r="J103" s="94"/>
-      <c r="K103" s="94"/>
+      <c r="H103" s="101"/>
+      <c r="I103" s="101"/>
+      <c r="J103" s="101"/>
+      <c r="K103" s="101"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:12">
       <c r="B104" s="4"/>
       <c r="C104" s="5"/>
       <c r="D104" s="5"/>
@@ -4008,7 +4911,7 @@
       <c r="G104" s="5"/>
       <c r="L104" s="6"/>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:12">
       <c r="B105" s="4"/>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
@@ -4018,39 +4921,39 @@
       <c r="H105" s="5"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:12">
       <c r="B106" s="4"/>
-      <c r="C106" s="130" t="s">
+      <c r="C106" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="D106" s="130"/>
-      <c r="E106" s="130"/>
-      <c r="F106" s="130"/>
+      <c r="D106" s="99"/>
+      <c r="E106" s="99"/>
+      <c r="F106" s="99"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="L106" s="6"/>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:12">
       <c r="B107" s="4"/>
-      <c r="C107" s="130"/>
-      <c r="D107" s="130"/>
-      <c r="E107" s="130"/>
-      <c r="F107" s="130"/>
+      <c r="C107" s="99"/>
+      <c r="D107" s="99"/>
+      <c r="E107" s="99"/>
+      <c r="F107" s="99"/>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="L107" s="6"/>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:12">
       <c r="B108" s="4"/>
-      <c r="C108" s="130"/>
-      <c r="D108" s="130"/>
-      <c r="E108" s="130"/>
-      <c r="F108" s="130"/>
+      <c r="C108" s="99"/>
+      <c r="D108" s="99"/>
+      <c r="E108" s="99"/>
+      <c r="F108" s="99"/>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
       <c r="L108" s="6"/>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:12">
       <c r="B109" s="4"/>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
@@ -4060,7 +4963,7 @@
       <c r="H109" s="5"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:12">
       <c r="B110" s="4"/>
       <c r="C110" s="5"/>
       <c r="D110" s="5"/>
@@ -4070,7 +4973,7 @@
       <c r="H110" s="5"/>
       <c r="L110" s="6"/>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:12">
       <c r="B111" s="4"/>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
@@ -4080,7 +4983,7 @@
       <c r="H111" s="5"/>
       <c r="L111" s="6"/>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:12">
       <c r="B112" s="4"/>
       <c r="C112" s="5"/>
       <c r="D112" s="5"/>
@@ -4090,7 +4993,7 @@
       <c r="H112" s="5"/>
       <c r="L112" s="6"/>
     </row>
-    <row r="113" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:20">
       <c r="B113" s="4"/>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
@@ -4103,7 +5006,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="6"/>
     </row>
-    <row r="114" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:20">
       <c r="B114" s="4"/>
       <c r="C114" s="5"/>
       <c r="D114" s="5"/>
@@ -4116,7 +5019,7 @@
       <c r="K114" s="5"/>
       <c r="L114" s="6"/>
     </row>
-    <row r="115" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:20">
       <c r="B115" s="4"/>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -4129,7 +5032,7 @@
       <c r="K115" s="5"/>
       <c r="L115" s="6"/>
     </row>
-    <row r="116" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:20" ht="17" thickBot="1">
       <c r="B116" s="7"/>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
@@ -4142,21 +5045,21 @@
       <c r="K116" s="8"/>
       <c r="L116" s="9"/>
     </row>
-    <row r="120" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:20">
       <c r="P120" s="50"/>
       <c r="Q120" s="50"/>
       <c r="R120" s="50"/>
       <c r="S120" s="50"/>
       <c r="T120" s="50"/>
     </row>
-    <row r="121" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:20">
       <c r="P121" s="50"/>
       <c r="Q121" s="50"/>
       <c r="R121" s="50"/>
       <c r="S121" s="50"/>
       <c r="T121" s="50"/>
     </row>
-    <row r="122" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:20">
       <c r="P122" s="50"/>
       <c r="Q122" s="50"/>
       <c r="R122" s="50"/>
@@ -4165,12 +5068,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="C106:F108"/>
-    <mergeCell ref="C101:F103"/>
     <mergeCell ref="H101:K103"/>
     <mergeCell ref="C94:F97"/>
     <mergeCell ref="C28:E28"/>
@@ -4185,6 +5082,12 @@
     <mergeCell ref="C70:F71"/>
     <mergeCell ref="C74:F75"/>
     <mergeCell ref="C78:F79"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="C106:F108"/>
+    <mergeCell ref="C101:F103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4196,44 +5099,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4175203-3506-4C43-BA73-F5FEF8C710AC}">
   <dimension ref="C26:U71"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:21">
       <c r="Q26" s="50"/>
       <c r="R26" s="50"/>
       <c r="S26" s="50"/>
       <c r="T26" s="50"/>
       <c r="U26" s="50"/>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21">
       <c r="Q27" s="50"/>
       <c r="R27" s="50"/>
       <c r="S27" s="50"/>
       <c r="T27" s="50"/>
       <c r="U27" s="50"/>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21">
       <c r="Q28" s="50"/>
       <c r="R28" s="50"/>
       <c r="S28" s="50"/>
       <c r="T28" s="50"/>
       <c r="U28" s="50"/>
     </row>
-    <row r="29" spans="3:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:21" ht="16" customHeight="1">
       <c r="Q29" s="50"/>
       <c r="R29" s="50"/>
       <c r="S29" s="50"/>
       <c r="T29" s="50"/>
       <c r="U29" s="50"/>
     </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:21">
       <c r="Q30" s="50"/>
       <c r="R30" s="50"/>
       <c r="S30" s="50"/>
       <c r="T30" s="50"/>
       <c r="U30" s="50"/>
     </row>
-    <row r="31" spans="3:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:21" ht="17" thickBot="1">
       <c r="G31" t="s">
         <v>19</v>
       </c>
@@ -4247,7 +5150,7 @@
       <c r="T31" s="50"/>
       <c r="U31" s="50"/>
     </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:21">
       <c r="C32" s="70"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -4269,7 +5172,7 @@
       <c r="T32" s="50"/>
       <c r="U32" s="50"/>
     </row>
-    <row r="33" spans="3:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:21" ht="17" thickBot="1">
       <c r="C33" s="71"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -4293,7 +5196,7 @@
       <c r="T33" s="50"/>
       <c r="U33" s="50"/>
     </row>
-    <row r="34" spans="3:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:21" ht="17" thickBot="1">
       <c r="C34" s="71"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -4315,7 +5218,7 @@
       <c r="T34" s="50"/>
       <c r="U34" s="50"/>
     </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:21">
       <c r="C35" s="71"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -4335,7 +5238,7 @@
       <c r="T35" s="50"/>
       <c r="U35" s="50"/>
     </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:21">
       <c r="C36" s="71"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -4357,7 +5260,7 @@
       <c r="T36" s="50"/>
       <c r="U36" s="50"/>
     </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:21">
       <c r="C37" s="71"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -4375,7 +5278,7 @@
       <c r="T37" s="50"/>
       <c r="U37" s="50"/>
     </row>
-    <row r="38" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:21">
       <c r="C38" s="71"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -4391,7 +5294,7 @@
       <c r="T38" s="50"/>
       <c r="U38" s="50"/>
     </row>
-    <row r="39" spans="3:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:21" ht="17" thickBot="1">
       <c r="C39" s="71"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -4411,7 +5314,7 @@
       <c r="T39" s="50"/>
       <c r="U39" s="50"/>
     </row>
-    <row r="40" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:21">
       <c r="C40" s="71"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -4431,7 +5334,7 @@
       <c r="T40" s="50"/>
       <c r="U40" s="50"/>
     </row>
-    <row r="41" spans="3:21" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:21" ht="16" customHeight="1" thickBot="1">
       <c r="C41" s="71"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -4453,7 +5356,7 @@
       <c r="T41" s="50"/>
       <c r="U41" s="50"/>
     </row>
-    <row r="42" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:21">
       <c r="C42" s="71"/>
       <c r="D42" s="51"/>
       <c r="E42" s="5"/>
@@ -4466,7 +5369,7 @@
       <c r="L42" s="56"/>
       <c r="M42" s="6"/>
     </row>
-    <row r="43" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:21">
       <c r="C43" s="71"/>
       <c r="D43" s="52"/>
       <c r="E43" s="5"/>
@@ -4479,7 +5382,7 @@
       <c r="L43" s="56"/>
       <c r="M43" s="6"/>
     </row>
-    <row r="44" spans="3:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:21" ht="17" thickBot="1">
       <c r="C44" s="71"/>
       <c r="D44" s="52"/>
       <c r="E44" s="5"/>
@@ -4492,7 +5395,7 @@
       <c r="L44" s="56"/>
       <c r="M44" s="6"/>
     </row>
-    <row r="45" spans="3:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:21" ht="17" thickBot="1">
       <c r="C45" s="71"/>
       <c r="D45" s="52"/>
       <c r="E45" s="5"/>
@@ -4507,7 +5410,7 @@
       <c r="L45" s="30"/>
       <c r="M45" s="6"/>
     </row>
-    <row r="46" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:21">
       <c r="C46" s="71"/>
       <c r="D46" s="52"/>
       <c r="E46" s="5"/>
@@ -4520,7 +5423,7 @@
       <c r="L46" s="5"/>
       <c r="M46" s="6"/>
     </row>
-    <row r="47" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:21">
       <c r="C47" s="71"/>
       <c r="D47" s="52"/>
       <c r="E47" s="5"/>
@@ -4533,7 +5436,7 @@
       <c r="L47" s="5"/>
       <c r="M47" s="6"/>
     </row>
-    <row r="48" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:21">
       <c r="C48" s="71"/>
       <c r="D48" s="52"/>
       <c r="E48" s="5"/>
@@ -4546,7 +5449,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="6"/>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14">
       <c r="C49" s="71"/>
       <c r="D49" s="52"/>
       <c r="E49" s="5"/>
@@ -4555,7 +5458,7 @@
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
-    <row r="50" spans="3:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" ht="17" thickBot="1">
       <c r="C50" s="71"/>
       <c r="D50" s="52"/>
       <c r="E50" s="5"/>
@@ -4564,7 +5467,7 @@
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
-    <row r="51" spans="3:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:14" ht="17" thickBot="1">
       <c r="C51" s="71"/>
       <c r="D51" s="52"/>
       <c r="E51" s="5"/>
@@ -4577,7 +5480,7 @@
       <c r="L51" s="59"/>
       <c r="M51" s="6"/>
     </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:14">
       <c r="C52" s="71"/>
       <c r="D52" s="52"/>
       <c r="E52" s="5"/>
@@ -4594,7 +5497,7 @@
       <c r="L52" s="61"/>
       <c r="M52" s="6"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14">
       <c r="C53" s="71"/>
       <c r="D53" s="52"/>
       <c r="E53" s="5"/>
@@ -4612,7 +5515,7 @@
       <c r="M53" s="5"/>
       <c r="N53" s="68"/>
     </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:14">
       <c r="C54" s="71"/>
       <c r="D54" s="52"/>
       <c r="E54" s="5"/>
@@ -4625,7 +5528,7 @@
       <c r="L54" s="61"/>
       <c r="M54" s="6"/>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14">
       <c r="C55" s="71"/>
       <c r="D55" s="52"/>
       <c r="E55" s="5"/>
@@ -4638,7 +5541,7 @@
       <c r="L55" s="61"/>
       <c r="M55" s="6"/>
     </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:14">
       <c r="C56" s="71" t="s">
         <v>33</v>
       </c>
@@ -4655,7 +5558,7 @@
       <c r="L56" s="61"/>
       <c r="M56" s="6"/>
     </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:14">
       <c r="C57" s="71" t="s">
         <v>32</v>
       </c>
@@ -4672,7 +5575,7 @@
       <c r="L57" s="61"/>
       <c r="M57" s="6"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14">
       <c r="C58" s="71" t="s">
         <v>24</v>
       </c>
@@ -4689,7 +5592,7 @@
       <c r="L58" s="61"/>
       <c r="M58" s="6"/>
     </row>
-    <row r="59" spans="3:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" ht="17" thickBot="1">
       <c r="C59" s="71" t="s">
         <v>23</v>
       </c>
@@ -4706,7 +5609,7 @@
       <c r="L59" s="61"/>
       <c r="M59" s="6"/>
     </row>
-    <row r="60" spans="3:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" ht="17" thickBot="1">
       <c r="C60" s="71" t="s">
         <v>20</v>
       </c>
@@ -4723,7 +5626,7 @@
       <c r="L60" s="64"/>
       <c r="M60" s="6"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14">
       <c r="C61" s="71"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -4736,7 +5639,7 @@
       <c r="L61" s="5"/>
       <c r="M61" s="6"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14">
       <c r="C62" s="71"/>
       <c r="D62" s="5" t="s">
         <v>13</v>
@@ -4752,7 +5655,7 @@
       <c r="L62" s="5"/>
       <c r="M62" s="6"/>
     </row>
-    <row r="63" spans="3:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" ht="17" thickBot="1">
       <c r="C63" s="72"/>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -4765,7 +5668,7 @@
       <c r="L63" s="8"/>
       <c r="M63" s="9"/>
     </row>
-    <row r="71" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="10:10">
       <c r="J71" s="85"/>
     </row>
   </sheetData>
@@ -4778,14 +5681,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942967D4-1223-2F4A-B092-299AED6C3185}">
   <dimension ref="B3:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="17" thickBot="1">
       <c r="F3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12">
       <c r="B4" s="70"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -4798,7 +5701,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="17" thickBot="1">
       <c r="B5" s="71"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -4813,7 +5716,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12">
       <c r="B6" s="71"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -4826,7 +5729,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12">
       <c r="B7" s="71"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -4843,7 +5746,7 @@
       <c r="K7" s="5"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12">
       <c r="B8" s="71"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -4860,7 +5763,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12">
       <c r="B9" s="71"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4873,7 +5776,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12">
       <c r="B10" s="71"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4886,7 +5789,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="17" thickBot="1">
       <c r="B11" s="71"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -4901,7 +5804,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12">
       <c r="B12" s="71"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -4918,7 +5821,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="17" thickBot="1">
       <c r="B13" s="71"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -4935,7 +5838,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12">
       <c r="B14" s="71"/>
       <c r="C14" s="51"/>
       <c r="D14" s="5"/>
@@ -4954,7 +5857,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12">
       <c r="B15" s="71"/>
       <c r="C15" s="52"/>
       <c r="D15" s="5"/>
@@ -4967,7 +5870,7 @@
       <c r="K15" s="5"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="17" thickBot="1">
       <c r="B16" s="71"/>
       <c r="C16" s="52"/>
       <c r="D16" s="5"/>
@@ -4980,7 +5883,7 @@
       <c r="K16" s="5"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" ht="17" thickBot="1">
       <c r="B17" s="71"/>
       <c r="C17" s="52"/>
       <c r="D17" s="5"/>
@@ -4995,7 +5898,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13">
       <c r="B18" s="71"/>
       <c r="C18" s="52"/>
       <c r="D18" s="5"/>
@@ -5008,7 +5911,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13">
       <c r="B19" s="71"/>
       <c r="C19" s="52"/>
       <c r="D19" s="5"/>
@@ -5021,7 +5924,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13">
       <c r="B20" s="71"/>
       <c r="C20" s="52"/>
       <c r="D20" s="5"/>
@@ -5034,7 +5937,7 @@
       <c r="K20" s="5"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13">
       <c r="B21" s="71"/>
       <c r="C21" s="52"/>
       <c r="D21" s="5"/>
@@ -5047,7 +5950,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" ht="17" thickBot="1">
       <c r="B22" s="71"/>
       <c r="C22" s="52"/>
       <c r="D22" s="5"/>
@@ -5060,7 +5963,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" ht="17" thickBot="1">
       <c r="B23" s="71"/>
       <c r="C23" s="52"/>
       <c r="D23" s="5"/>
@@ -5073,7 +5976,7 @@
       <c r="K23" s="59"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13">
       <c r="B24" s="71"/>
       <c r="C24" s="52"/>
       <c r="D24" s="5"/>
@@ -5090,7 +5993,7 @@
       <c r="K24" s="61"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13">
       <c r="B25" s="71"/>
       <c r="C25" s="52"/>
       <c r="D25" s="5"/>
@@ -5108,7 +6011,7 @@
       <c r="L25" s="6"/>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13">
       <c r="B26" s="71"/>
       <c r="C26" s="52"/>
       <c r="D26" s="5"/>
@@ -5125,7 +6028,7 @@
       <c r="K26" s="61"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13">
       <c r="B27" s="71"/>
       <c r="C27" s="52"/>
       <c r="D27" s="5"/>
@@ -5138,7 +6041,7 @@
       <c r="K27" s="61"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13">
       <c r="B28" s="71"/>
       <c r="C28" s="52"/>
       <c r="D28" s="5"/>
@@ -5151,7 +6054,7 @@
       <c r="K28" s="61"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:13">
       <c r="B29" s="71"/>
       <c r="C29" s="52"/>
       <c r="D29" s="5"/>
@@ -5164,7 +6067,7 @@
       <c r="K29" s="61"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:13">
       <c r="B30" s="71" t="s">
         <v>41</v>
       </c>
@@ -5181,7 +6084,7 @@
       <c r="K30" s="61"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="17" thickBot="1">
       <c r="B31" s="71" t="s">
         <v>38</v>
       </c>
@@ -5198,7 +6101,7 @@
       <c r="K31" s="61"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" ht="17" thickBot="1">
       <c r="B32" s="71" t="s">
         <v>37</v>
       </c>
@@ -5215,7 +6118,7 @@
       <c r="K32" s="64"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12">
       <c r="B33" s="71"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -5228,7 +6131,7 @@
       <c r="K33" s="5"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12">
       <c r="B34" s="71"/>
       <c r="C34" s="5" t="s">
         <v>13</v>
@@ -5245,7 +6148,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" ht="17" thickBot="1">
       <c r="B35" s="72"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -5262,4 +6165,510 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7F2BF1-493F-CC46-B5F1-32EAE8890DEE}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="8" width="10.83203125" style="132"/>
+    <col min="9" max="9" width="10.83203125" style="133"/>
+    <col min="10" max="16384" width="10.83203125" style="132"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="148" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="D4" s="132" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="17" thickBot="1"/>
+    <row r="7" spans="1:11" ht="17" thickBot="1">
+      <c r="H7" s="147"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="144"/>
+    </row>
+    <row r="8" spans="1:11" ht="17" thickBot="1">
+      <c r="D8" s="143"/>
+      <c r="H8" s="140"/>
+      <c r="K8" s="139"/>
+    </row>
+    <row r="9" spans="1:11" ht="17" thickBot="1">
+      <c r="D9" s="141"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="142">
+        <v>3</v>
+      </c>
+      <c r="K9" s="139"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="D10" s="141"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="133" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="139"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="D11" s="141"/>
+      <c r="H11" s="140"/>
+      <c r="K11" s="139"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="D12" s="141"/>
+      <c r="H12" s="140"/>
+      <c r="K12" s="139"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="D13" s="141"/>
+      <c r="H13" s="140"/>
+      <c r="K13" s="139"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="D14" s="141"/>
+      <c r="H14" s="140"/>
+      <c r="K14" s="139"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="D15" s="141"/>
+      <c r="H15" s="140"/>
+      <c r="K15" s="139"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="D16" s="141"/>
+      <c r="H16" s="140"/>
+      <c r="K16" s="139"/>
+    </row>
+    <row r="17" spans="3:11">
+      <c r="D17" s="141"/>
+      <c r="H17" s="140"/>
+      <c r="K17" s="139"/>
+    </row>
+    <row r="18" spans="3:11">
+      <c r="D18" s="141"/>
+      <c r="H18" s="140"/>
+      <c r="K18" s="139"/>
+    </row>
+    <row r="19" spans="3:11">
+      <c r="D19" s="141"/>
+      <c r="H19" s="140"/>
+      <c r="K19" s="139"/>
+    </row>
+    <row r="20" spans="3:11">
+      <c r="D20" s="141"/>
+      <c r="H20" s="140"/>
+      <c r="K20" s="139"/>
+    </row>
+    <row r="21" spans="3:11">
+      <c r="D21" s="141"/>
+      <c r="H21" s="140"/>
+      <c r="K21" s="139"/>
+    </row>
+    <row r="22" spans="3:11" ht="17" thickBot="1">
+      <c r="C22" s="132" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="138" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="137"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="134"/>
+    </row>
+    <row r="25" spans="3:11">
+      <c r="D25" s="132" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="133" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Home!B34" display="Home" xr:uid="{C17CCE1E-0EF0-5843-9C2B-222A36418B74}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3484FEB8-F6E4-F84C-81B2-EEE097F10CF2}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="9" style="159"/>
+    <col min="2" max="2" width="13" style="159" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="159" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5" style="159" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="159"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15">
+      <c r="A1" s="170" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="164" customFormat="1">
+      <c r="B3" s="169" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="169" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="169" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="164" customFormat="1" ht="13">
+      <c r="B4" s="166" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="166" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="165" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="164" customFormat="1" ht="13">
+      <c r="B5" s="167" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="168" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="167" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="164" customFormat="1">
+      <c r="B6" s="167" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="167" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="167" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="164" customFormat="1" ht="13">
+      <c r="B7" s="166" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="165" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="165" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="160"/>
+      <c r="B8" s="160"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+    </row>
+    <row r="9" spans="1:5" ht="13">
+      <c r="A9" s="160"/>
+      <c r="B9" s="163" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+    </row>
+    <row r="10" spans="1:5" ht="13">
+      <c r="A10" s="160"/>
+      <c r="B10" s="162" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="160"/>
+      <c r="B11" s="161" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="160"/>
+      <c r="B12" s="160"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="160"/>
+      <c r="B13" s="160"/>
+      <c r="C13" s="160"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="160"/>
+      <c r="B14" s="160"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="160"/>
+      <c r="B15" s="160"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="160"/>
+      <c r="B16" s="160"/>
+      <c r="C16" s="160"/>
+      <c r="D16" s="160"/>
+      <c r="E16" s="160"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="160"/>
+      <c r="B17" s="160"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="160"/>
+      <c r="B18" s="160"/>
+      <c r="C18" s="160"/>
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="160"/>
+      <c r="B19" s="160"/>
+      <c r="C19" s="160"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="160"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="160"/>
+      <c r="B20" s="160"/>
+      <c r="C20" s="160"/>
+      <c r="D20" s="160"/>
+      <c r="E20" s="160"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="160"/>
+      <c r="B21" s="160"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Home!B23" display="Home" xr:uid="{36251F4B-9438-8D48-A204-7BFE5EDFFD7E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C592EE7-209E-864C-872A-20E8A3EE1BED}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" style="149"/>
+    <col min="2" max="2" width="32.6640625" style="149" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="149"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16" thickBot="1">
+      <c r="A1" s="148" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="H2" s="158"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="156"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="H3" s="154"/>
+      <c r="K3" s="153"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="H4" s="154"/>
+      <c r="I4" s="149" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="153"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="H5" s="154"/>
+      <c r="K5" s="153"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="H6" s="154"/>
+      <c r="K6" s="153"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="H7" s="154"/>
+      <c r="K7" s="149" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="H8" s="154"/>
+      <c r="K8" s="153"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="H9" s="154"/>
+      <c r="K9" s="153"/>
+    </row>
+    <row r="10" spans="1:11" ht="16" thickBot="1">
+      <c r="B10" s="149" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="152"/>
+      <c r="I10" s="151"/>
+      <c r="J10" s="151"/>
+      <c r="K10" s="150"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="149" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="149" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="149" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="149" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="16" thickBot="1">
+      <c r="B14" s="149" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="16" thickBot="1">
+      <c r="D15" s="158"/>
+      <c r="E15" s="156"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="157"/>
+      <c r="J15" s="157"/>
+      <c r="K15" s="156"/>
+    </row>
+    <row r="16" spans="1:11" ht="16" thickBot="1">
+      <c r="D16" s="154" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="153" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="154"/>
+      <c r="I16" s="155" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="153"/>
+    </row>
+    <row r="17" spans="4:11" ht="16" thickBot="1">
+      <c r="D17" s="154" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="153" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="154"/>
+      <c r="K17" s="153"/>
+    </row>
+    <row r="18" spans="4:11" ht="16" thickBot="1">
+      <c r="D18" s="154" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="153" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="154"/>
+      <c r="I18" s="155" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="153"/>
+    </row>
+    <row r="19" spans="4:11" ht="16" thickBot="1">
+      <c r="D19" s="154" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="154"/>
+      <c r="K19" s="153"/>
+    </row>
+    <row r="20" spans="4:11" ht="16" thickBot="1">
+      <c r="D20" s="154" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="153" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="154"/>
+      <c r="I20" s="155" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="153"/>
+    </row>
+    <row r="21" spans="4:11">
+      <c r="D21" s="154"/>
+      <c r="E21" s="153"/>
+      <c r="H21" s="154"/>
+      <c r="K21" s="153"/>
+    </row>
+    <row r="22" spans="4:11" ht="16" thickBot="1">
+      <c r="D22" s="152"/>
+      <c r="E22" s="150"/>
+      <c r="H22" s="154"/>
+      <c r="K22" s="153"/>
+    </row>
+    <row r="23" spans="4:11" ht="16" thickBot="1">
+      <c r="H23" s="152"/>
+      <c r="I23" s="151"/>
+      <c r="J23" s="151"/>
+      <c r="K23" s="150"/>
+    </row>
+    <row r="24" spans="4:11">
+      <c r="D24" s="149" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11">
+      <c r="I25" s="149" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Home!B22" display="Home" xr:uid="{BFF248D1-4105-6945-884D-19E5BB988C31}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>